--- a/accountant_forms/006_payment_form_template--accountant_forms.xlsx
+++ b/accountant_forms/006_payment_form_template--accountant_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'credit_card_type_1',_'label':_'credit_card_type_1'}</t>
+          <t>credit_card_type_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 'credit_card_type_1', 'label': 'credit_card_type_1'}</t>
+          <t>credit card type 1</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'credit_card_type_2',_'label':_'credit_card_type_2'}</t>
+          <t>credit_card_type_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 'credit_card_type_2', 'label': 'credit_card_type_2'}</t>
+          <t>credit card type 2</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'credit_card_type_3',_'label':_'credit_card_type_3'}</t>
+          <t>credit_card_type_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 'credit_card_type_3', 'label': 'credit_card_type_3'}</t>
+          <t>credit card type 3</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'exp_month_1',_'label':_'exp_month_1'}</t>
+          <t>exp_month_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 'exp_month_1', 'label': 'exp_month_1'}</t>
+          <t>exp month 1</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'exp_month_2',_'label':_'exp_month_2'}</t>
+          <t>exp_month_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 'exp_month_2', 'label': 'exp_month_2'}</t>
+          <t>exp month 2</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'exp_month_3',_'label':_'exp_month_3'}</t>
+          <t>exp_month_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 'exp_month_3', 'label': 'exp_month_3'}</t>
+          <t>exp month 3</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'exp_year_1',_'label':_'exp_year_1'}</t>
+          <t>exp_year_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 'exp_year_1', 'label': 'exp_year_1'}</t>
+          <t>exp year 1</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'exp_year_2',_'label':_'exp_year_2'}</t>
+          <t>exp_year_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 'exp_year_2', 'label': 'exp_year_2'}</t>
+          <t>exp year 2</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'exp_year_3',_'label':_'exp_year_3'}</t>
+          <t>exp_year_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 'exp_year_3', 'label': 'exp_year_3'}</t>
+          <t>exp year 3</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'payment_method_1',_'label':_'payment_method_1'}</t>
+          <t>payment_method_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 'payment_method_1', 'label': 'payment_method_1'}</t>
+          <t>payment method 1</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'payment_method_2',_'label':_'payment_method_2'}</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 'payment_method_2', 'label': 'payment_method_2'}</t>
+          <t>payment method 2</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'payment_method_3',_'label':_'payment_method_3'}</t>
+          <t>payment_method_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 'payment_method_3', 'label': 'payment_method_3'}</t>
+          <t>payment method 3</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'payment_currency_1',_'label':_'payment_currency_1'}</t>
+          <t>payment_currency_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 'payment_currency_1', 'label': 'payment_currency_1'}</t>
+          <t>payment currency 1</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'payment_currency_2',_'label':_'payment_currency_2'}</t>
+          <t>payment_currency_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 'payment_currency_2', 'label': 'payment_currency_2'}</t>
+          <t>payment currency 2</t>
         </is>
       </c>
     </row>
